--- a/interface/linear/only_table/linear_regression_table.xlsx
+++ b/interface/linear/only_table/linear_regression_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yue\Desktop\newPeng\Peng1.0_GUI\interface\linear\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yue\Desktop\newPeng\Peng1.0_GUI\interface\linear\only_table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAE7FDE-BD80-49BD-A528-847E9022A57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4367A62D-3E7F-410D-81EB-F41D05D0CC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="4040" windowWidth="25020" windowHeight="16430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3480" yWindow="4450" windowWidth="25000" windowHeight="16430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/interface/linear/only_table/linear_regression_table.xlsx
+++ b/interface/linear/only_table/linear_regression_table.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yue\Desktop\newPeng\Peng1.0_GUI\interface\linear\only_table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yue\Desktop\wangkechun\Peng1.0_GUI\interface\linear\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4367A62D-3E7F-410D-81EB-F41D05D0CC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C488CB-449D-4313-AB7C-FFABB644B5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="4450" windowWidth="25000" windowHeight="16430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="5510" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -45,19 +54,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,19 +104,237 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -118,9 +347,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -128,42 +357,42 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -192,12 +421,13 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -226,171 +456,135 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -402,10 +596,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,89 +616,106 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>123.72123893805311</v>
-      </c>
-      <c r="D2">
-        <v>169.17711406096359</v>
-      </c>
-      <c r="E2">
-        <v>198.82300884955751</v>
+      <c r="C2" s="2">
+        <v>71.648809523809504</v>
+      </c>
+      <c r="D2" s="2">
+        <v>163.64880952380901</v>
+      </c>
+      <c r="E2" s="2">
+        <v>184.64880952380901</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>40</v>
-      </c>
-      <c r="C3">
-        <v>139.8704044117647</v>
-      </c>
-      <c r="D3">
-        <v>173.320575105042</v>
-      </c>
-      <c r="E3">
-        <v>201.39699317226891</v>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>81.040878451837401</v>
+      </c>
+      <c r="D3" s="2">
+        <v>167.887366818874</v>
+      </c>
+      <c r="E3" s="2">
+        <v>184.90911067623401</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>80</v>
-      </c>
-      <c r="C4">
-        <v>152.87600818586731</v>
-      </c>
-      <c r="D4">
-        <v>168.4463705308776</v>
-      </c>
-      <c r="E4">
-        <v>198.05116167087999</v>
+      <c r="B4" s="2">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>86.904952581664901</v>
+      </c>
+      <c r="D4" s="2">
+        <v>168.262802950474</v>
+      </c>
+      <c r="E4" s="2">
+        <v>184.189251844046</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>120</v>
-      </c>
-      <c r="C5">
-        <v>160.40152294710839</v>
-      </c>
-      <c r="D5">
-        <v>170.99471770597521</v>
-      </c>
-      <c r="E5">
-        <v>196.94381559991771</v>
+      <c r="B5" s="2">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>98.480218855218894</v>
+      </c>
+      <c r="D5" s="2">
+        <v>170.48021885521899</v>
+      </c>
+      <c r="E5" s="2">
+        <v>184.48021885521899</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>160</v>
-      </c>
-      <c r="C6">
-        <v>173.52512224505699</v>
-      </c>
-      <c r="D6">
-        <v>175.02515767840691</v>
-      </c>
-      <c r="E6">
-        <v>199.25228545106651</v>
+      <c r="B6" s="2">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2">
+        <v>109.148290598291</v>
+      </c>
+      <c r="D6" s="2">
+        <v>171.63183760683799</v>
+      </c>
+      <c r="E6" s="2">
+        <v>182.15662393162401</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2">
+        <v>118.57044534412999</v>
+      </c>
+      <c r="D7" s="2">
+        <v>175.84493927125499</v>
+      </c>
+      <c r="E7" s="2">
+        <v>182.021457489878</v>
       </c>
     </row>
   </sheetData>
